--- a/artfynd/A 6317-2023 artfynd.xlsx
+++ b/artfynd/A 6317-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115132349</v>
+        <v>73175970</v>
       </c>
       <c r="B2" t="n">
-        <v>57215</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,49 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102621</v>
+        <v>4769</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Holan, Bjursås, Dlr</t>
+          <t>Bjursås prästskog NR, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525510</v>
+        <v>525402</v>
       </c>
       <c r="R2" t="n">
-        <v>6733313</v>
+        <v>6733249</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +742,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2018-09-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2018-09-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>massor</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,21 +761,280 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>fuktigt med tussilago</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>myrstack</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>115132349</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57794</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Holan, Bjursås, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>525510</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6733313</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Birger Roos</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Birger Roos</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132977849</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101974</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Prästskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>525367</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6733312</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Henrik Sund</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Henrik Sund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6317-2023 artfynd.xlsx
+++ b/artfynd/A 6317-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73175970</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -911,6 +921,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115132349</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1035,8 +1050,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132977849</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>